--- a/exports/SUNPHARMA_full_report.xlsx
+++ b/exports/SUNPHARMA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>4.2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>836.9</v>
+        <v>824</v>
       </c>
       <c r="I2" t="n">
         <v>824.99604320555</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.17</v>
+        <v>-0.39</v>
       </c>
       <c r="L2" t="n">
         <v>1.16</v>
@@ -555,7 +578,7 @@
         <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.31</v>
+        <v>1.79</v>
       </c>
       <c r="O2" t="n">
         <v>-0.54</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>5.8</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44592.55208333334</v>
+        <v>44593.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>834</v>
+        <v>876.55</v>
       </c>
       <c r="I3" t="n">
         <v>839.9550634423816</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.21</v>
+        <v>-6.38</v>
       </c>
       <c r="L3" t="n">
-        <v>3.09</v>
+        <v>7.76</v>
       </c>
       <c r="M3" t="n">
-        <v>0.72</v>
+        <v>1.61</v>
       </c>
       <c r="N3" t="n">
-        <v>2.38</v>
+        <v>6.81</v>
       </c>
       <c r="O3" t="n">
         <v>-1.79</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.49</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.38541666666</v>
+        <v>44613.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>853.9</v>
+        <v>845</v>
       </c>
       <c r="I4" t="n">
         <v>851.5398639677296</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.58</v>
+        <v>-3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>3.92</v>
+        <v>4.23</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>4.65</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44628.55208333334</v>
+        <v>44629.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>855.9</v>
+        <v>880.25</v>
       </c>
       <c r="I5" t="n">
         <v>863.6013440847615</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.29</v>
+        <v>-4.17</v>
       </c>
       <c r="L5" t="n">
-        <v>1.92</v>
+        <v>4.82</v>
       </c>
       <c r="M5" t="n">
         <v>1.55</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.06</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44686.38541666666</v>
+        <v>44686.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>903</v>
+        <v>873.25</v>
       </c>
       <c r="I6" t="n">
         <v>900.1400395027305</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>2.58</v>
+        <v>-0.8</v>
       </c>
       <c r="L6" t="n">
         <v>2.3</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>8.4</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>884.95</v>
+        <v>909.75</v>
       </c>
       <c r="I7" t="n">
         <v>902.2409861546532</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.34</v>
+        <v>-4.18</v>
       </c>
       <c r="L7" t="n">
-        <v>4.09</v>
+        <v>4.79</v>
       </c>
       <c r="M7" t="n">
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
         <v>-3.29</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>6.55</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44711.55208333334</v>
+        <v>44712.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>888</v>
+        <v>858.7</v>
       </c>
       <c r="I8" t="n">
         <v>876.7289151033768</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.39</v>
+        <v>-5.61</v>
       </c>
       <c r="L8" t="n">
-        <v>2.56</v>
+        <v>6.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01</v>
+        <v>2.34</v>
       </c>
       <c r="N8" t="n">
-        <v>1.76</v>
+        <v>3.03</v>
       </c>
       <c r="O8" t="n">
         <v>3.4</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.03</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>823.25</v>
+        <v>843.7</v>
       </c>
       <c r="I9" t="n">
         <v>835.8146298966712</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>4.13</v>
+        <v>1.75</v>
       </c>
       <c r="L9" t="n">
         <v>2.78</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.38</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>900.5</v>
+        <v>886.6</v>
       </c>
       <c r="I10" t="n">
         <v>891.4083702029496</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K10" t="n">
-        <v>6.73</v>
+        <v>5.08</v>
       </c>
       <c r="L10" t="n">
         <v>2.57</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>4.97</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44824.38541666666</v>
+        <v>44824.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>897.85</v>
+        <v>911.3</v>
       </c>
       <c r="I11" t="n">
         <v>901.7357789716524</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.27</v>
+        <v>-2.79</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>3.16</v>
       </c>
       <c r="M11" t="n">
         <v>0.75</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.33</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1007</v>
+        <v>996.1</v>
       </c>
       <c r="I12" t="n">
         <v>1001.841295823028</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>59</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>10.5</v>
+        <v>9.31</v>
       </c>
       <c r="L12" t="n">
         <v>2.07</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>4.69</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44893.55208333334</v>
+        <v>44894.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1037</v>
+        <v>1040.3</v>
       </c>
       <c r="I13" t="n">
         <v>1037.755781473196</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.11</v>
+        <v>-4.44</v>
       </c>
       <c r="L13" t="n">
-        <v>4.54</v>
+        <v>5.19</v>
       </c>
       <c r="M13" t="n">
         <v>0.42</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>3.12</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44902.55208333334</v>
+        <v>44903.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1018.9</v>
+        <v>981.8</v>
       </c>
       <c r="I14" t="n">
         <v>1015.90271670197</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.06</v>
+        <v>-5.62</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>5.95</v>
       </c>
       <c r="M14" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="N14" t="n">
-        <v>1.56</v>
+        <v>3.82</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.23</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44936.55208333334</v>
+        <v>44937.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1012.95</v>
+        <v>1029</v>
       </c>
       <c r="I15" t="n">
         <v>1018.332680644246</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.17</v>
+        <v>-4.81</v>
       </c>
       <c r="L15" t="n">
         <v>5.32</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>4.69</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1051</v>
+        <v>1010.2</v>
       </c>
       <c r="I16" t="n">
         <v>1013.547843213796</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>2.14</v>
+        <v>-1.83</v>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="M16" t="n">
-        <v>0.93</v>
+        <v>1.38</v>
       </c>
       <c r="N16" t="n">
-        <v>0.96</v>
+        <v>3.43</v>
       </c>
       <c r="O16" t="n">
         <v>1.29</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.4</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45009.55208333334</v>
+        <v>45012.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>973</v>
+        <v>985.3</v>
       </c>
       <c r="I17" t="n">
         <v>983.9868374126326</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K17" t="n">
-        <v>3.68</v>
+        <v>2.46</v>
       </c>
       <c r="L17" t="n">
         <v>3.14</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>4.31</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45037.55208333334</v>
+        <v>45040.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>986.9</v>
+        <v>970.35</v>
       </c>
       <c r="I18" t="n">
         <v>983.8848308103318</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>0.16</v>
+        <v>-1.52</v>
       </c>
       <c r="L18" t="n">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="M18" t="n">
-        <v>0.43</v>
+        <v>1.21</v>
       </c>
       <c r="N18" t="n">
         <v>1.48</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>3.35</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45072.38541666666</v>
+        <v>45072.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>944.65</v>
+        <v>967</v>
       </c>
       <c r="I19" t="n">
         <v>954.5298279758506</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>2.65</v>
+        <v>0.35</v>
       </c>
       <c r="L19" t="n">
         <v>2.28</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.46</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1140</v>
+        <v>1116.5</v>
       </c>
       <c r="I20" t="n">
         <v>1122.845196194221</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>130</v>
+        <v>130.8333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>17.89</v>
+        <v>15.46</v>
       </c>
       <c r="L20" t="n">
         <v>2.33</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>177</v>
+        <v>178</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>4.67</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1132</v>
+        <v>1144.45</v>
       </c>
       <c r="I21" t="n">
         <v>1139.762435277655</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.39</v>
+        <v>-2.5</v>
       </c>
       <c r="L21" t="n">
         <v>4.06</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.33</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1585</v>
+        <v>1550.1</v>
       </c>
       <c r="I22" t="n">
         <v>1556.083005838986</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>130.1666666666667</v>
+        <v>131</v>
       </c>
       <c r="K22" t="n">
-        <v>38.49</v>
+        <v>35.44</v>
       </c>
       <c r="L22" t="n">
         <v>1.13</v>
@@ -1695,7 +1958,7 @@
         <v>1.15</v>
       </c>
       <c r="N22" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="O22" t="n">
         <v>0.87</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>5.4</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45373.38541666666</v>
+        <v>45373.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1605.4</v>
+        <v>1616</v>
       </c>
       <c r="I23" t="n">
         <v>1609.828937841745</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.57</v>
+        <v>-4.25</v>
       </c>
       <c r="L23" t="n">
-        <v>3.79</v>
+        <v>4.57</v>
       </c>
       <c r="M23" t="n">
         <v>0.91</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>4.61</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45392.55208333334</v>
+        <v>45394.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1606</v>
+        <v>1539.95</v>
       </c>
       <c r="I24" t="n">
         <v>1565.865128877152</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>19</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.62</v>
+        <v>-4.71</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>4.89</v>
       </c>
       <c r="M24" t="n">
         <v>1.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.87</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>3.26</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.35</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45434.38541666666</v>
+        <v>45434.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1517.1</v>
+        <v>1561.95</v>
       </c>
       <c r="I25" t="n">
         <v>1559.634353809429</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K25" t="n">
-        <v>1.48</v>
+        <v>-1.43</v>
       </c>
       <c r="L25" t="n">
         <v>3.57</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>6.52</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45442.55208333334</v>
+        <v>45443.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1465.2</v>
+        <v>1443.05</v>
       </c>
       <c r="I26" t="n">
         <v>1460.139841492391</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.19</v>
+        <v>-7.61</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.68</v>
       </c>
       <c r="M26" t="n">
         <v>3.33</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.64</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45469.38541666666</v>
+        <v>45469.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1511.4</v>
+        <v>1523</v>
       </c>
       <c r="I27" t="n">
         <v>1522.619876389105</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.74</v>
+        <v>-5.54</v>
       </c>
       <c r="L27" t="n">
         <v>6.02</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>3.57</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45581.55208333334</v>
+        <v>45582.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1900.2</v>
+        <v>1882.5</v>
       </c>
       <c r="I28" t="n">
         <v>1887.433788883702</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>112</v>
+        <v>112.8333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>24.77</v>
+        <v>23.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.62</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.69</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45650.55208333334</v>
+        <v>45652.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1817.1</v>
+        <v>1826.35</v>
       </c>
       <c r="I29" t="n">
         <v>1822.788477988305</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>68.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K29" t="n">
-        <v>3.47</v>
+        <v>2.98</v>
       </c>
       <c r="L29" t="n">
         <v>2.19</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>3.61</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1830.05</v>
+        <v>1782.05</v>
       </c>
       <c r="I30" t="n">
         <v>1826.511412391709</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2</v>
+        <v>-2.43</v>
       </c>
       <c r="L30" t="n">
-        <v>0.68</v>
+        <v>2.62</v>
       </c>
       <c r="M30" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="N30" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="O30" t="n">
         <v>1.54</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>5.36</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45679.55208333334</v>
+        <v>45680.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1794</v>
+        <v>1835</v>
       </c>
       <c r="I31" t="n">
         <v>1816.532255551739</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.67</v>
+        <v>-2.97</v>
       </c>
       <c r="L31" t="n">
-        <v>2.95</v>
+        <v>3.23</v>
       </c>
       <c r="M31" t="n">
         <v>0.91</v>
       </c>
       <c r="N31" t="n">
-        <v>1.68</v>
+        <v>2.51</v>
       </c>
       <c r="O31" t="n">
         <v>-2.3</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.71</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45684.55208333334</v>
+        <v>45685.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1787.95</v>
+        <v>1707.2</v>
       </c>
       <c r="I32" t="n">
         <v>1756.50381549214</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.56</v>
+        <v>-6.96</v>
       </c>
       <c r="L32" t="n">
-        <v>3.31</v>
+        <v>7.73</v>
       </c>
       <c r="M32" t="n">
         <v>0.54</v>
       </c>
       <c r="N32" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="O32" t="n">
         <v>2.51</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.6</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45726.55208333334</v>
+        <v>45727.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1610</v>
+        <v>1655</v>
       </c>
       <c r="I33" t="n">
         <v>1644.941966440012</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K33" t="n">
-        <v>5.69</v>
+        <v>3.06</v>
       </c>
       <c r="L33" t="n">
         <v>4.79</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.24</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45742.55208333334</v>
+        <v>45743.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1750.05</v>
+        <v>1724.95</v>
       </c>
       <c r="I34" t="n">
         <v>1730.805916577764</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K34" t="n">
-        <v>5.74</v>
+        <v>4.23</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>4.74</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1698.3</v>
+        <v>1773.2</v>
       </c>
       <c r="I35" t="n">
         <v>1768.876757685243</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>1.54</v>
+        <v>-2.8</v>
       </c>
       <c r="L35" t="n">
-        <v>1.59</v>
+        <v>5.09</v>
       </c>
       <c r="M35" t="n">
-        <v>0.05</v>
+        <v>3.34</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="O35" t="n">
         <v>-0.9</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>5.38</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1710</v>
+        <v>1660.4</v>
       </c>
       <c r="I36" t="n">
         <v>1677.750918083281</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.56</v>
+        <v>-6.36</v>
       </c>
       <c r="L36" t="n">
-        <v>6.49</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>-0</v>
+        <v>5.26</v>
       </c>
       <c r="N36" t="n">
         <v>3.5</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.35</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45770.38541666666</v>
+        <v>45770.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1781.2</v>
+        <v>1785.2</v>
       </c>
       <c r="I37" t="n">
         <v>1782.462742645559</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.28</v>
+        <v>-7.52</v>
       </c>
       <c r="L37" t="n">
-        <v>7.31</v>
+        <v>7.88</v>
       </c>
       <c r="M37" t="n">
         <v>3.53</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>4.91</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>1772.2</v>
+        <v>1755</v>
       </c>
       <c r="I38" t="n">
         <v>1759.453611418358</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.73</v>
+        <v>-1.69</v>
       </c>
       <c r="L38" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="M38" t="n">
         <v>0.77</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>4.88</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45852.55208333334</v>
+        <v>45853.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1681.7</v>
+        <v>1725</v>
       </c>
       <c r="I39" t="n">
         <v>1702.254443824928</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>67</v>
+        <v>67.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>4.18</v>
+        <v>1.71</v>
       </c>
       <c r="L39" t="n">
         <v>1.28</v>
       </c>
       <c r="M39" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="N39" t="n">
-        <v>2.13</v>
+        <v>2.74</v>
       </c>
       <c r="O39" t="n">
         <v>-1.45</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>4.46</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1700</v>
+        <v>1624.2</v>
       </c>
       <c r="I40" t="n">
         <v>1688.052218199758</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.45</v>
+        <v>-5.84</v>
       </c>
       <c r="L40" t="n">
-        <v>3.11</v>
+        <v>6.78</v>
       </c>
       <c r="M40" t="n">
         <v>1.02</v>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>4.24</v>
       </c>
       <c r="O40" t="n">
         <v>2.74</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.71</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45894.38541666666</v>
+        <v>45894.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>1647.4</v>
+        <v>1658</v>
       </c>
       <c r="I41" t="n">
         <v>1657.602062009587</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.43</v>
+        <v>-2.08</v>
       </c>
       <c r="L41" t="n">
         <v>4.36</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>3.7</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1601.2</v>
+        <v>1579.2</v>
       </c>
       <c r="I42" t="n">
         <v>1596.616429414971</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.43</v>
+        <v>-4.75</v>
       </c>
       <c r="L42" t="n">
-        <v>3.73</v>
+        <v>5.45</v>
       </c>
       <c r="M42" t="n">
         <v>0.78</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>4.46</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45917.38541666666</v>
+        <v>45917.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1615.5</v>
+        <v>1620.8</v>
       </c>
       <c r="I43" t="n">
         <v>1619.131669467901</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.3</v>
+        <v>-2.63</v>
       </c>
       <c r="L43" t="n">
         <v>2.74</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>2.87</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1625</v>
+        <v>1581.2</v>
       </c>
       <c r="I44" t="n">
         <v>1613.091107383712</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K44" t="n">
-        <v>0.26</v>
+        <v>-2.44</v>
       </c>
       <c r="L44" t="n">
-        <v>0.46</v>
+        <v>4.49</v>
       </c>
       <c r="M44" t="n">
-        <v>0.48</v>
+        <v>2.46</v>
       </c>
       <c r="N44" t="n">
-        <v>1.3</v>
+        <v>2.46</v>
       </c>
       <c r="O44" t="n">
         <v>0.61</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>3.54</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45931.38541666666</v>
+        <v>45931.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>1631.3</v>
+        <v>1639</v>
       </c>
       <c r="I45" t="n">
         <v>1637.189980432101</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.17</v>
+        <v>-3.66</v>
       </c>
       <c r="L45" t="n">
         <v>4.45</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.26</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46000.38541666666</v>
+        <v>46000.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>1795.1</v>
+        <v>1774.2</v>
       </c>
       <c r="I46" t="n">
         <v>1781.0999525163</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>68.83333333333333</v>
+        <v>69</v>
       </c>
       <c r="K46" t="n">
-        <v>9.52</v>
+        <v>8.25</v>
       </c>
       <c r="L46" t="n">
         <v>2.38</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>3.51</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46028.55208333334</v>
+        <v>46029.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1760</v>
+        <v>1771.6</v>
       </c>
       <c r="I47" t="n">
         <v>1760.579622581009</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="L47" t="n">
         <v>2.12</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>3.12</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1727.9</v>
+        <v>1700.2</v>
       </c>
       <c r="I48" t="n">
         <v>1716.2965799327</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.47</v>
+        <v>-4.03</v>
       </c>
       <c r="L48" t="n">
-        <v>3.36</v>
+        <v>4.32</v>
       </c>
       <c r="M48" t="n">
         <v>0.93</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5.11</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1628.9</v>
+        <v>1706.8</v>
       </c>
       <c r="I49" t="n">
         <v>1670.607997900177</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>4.19</v>
+        <v>-0.39</v>
       </c>
       <c r="L49" t="n">
         <v>2.17</v>
       </c>
       <c r="M49" t="n">
-        <v>2.82</v>
+        <v>4.97</v>
       </c>
       <c r="N49" t="n">
-        <v>1.27</v>
+        <v>4.49</v>
       </c>
       <c r="O49" t="n">
         <v>-1.25</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.52</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46100.38541666666</v>
+        <v>46100.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1761</v>
+        <v>1749.6</v>
       </c>
       <c r="I50" t="n">
         <v>1760.314372482969</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>3.18</v>
+        <v>2.51</v>
       </c>
       <c r="L50" t="n">
         <v>2.1</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.09</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46136.55208333334</v>
+        <v>46139.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1618.5</v>
+        <v>1736.8</v>
       </c>
       <c r="I51" t="n">
         <v>1701.830839597639</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>36</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>7.49</v>
+        <v>0.73</v>
       </c>
       <c r="L51" t="n">
         <v>3.97</v>
@@ -3348,7 +3959,7 @@
         <v>1.6</v>
       </c>
       <c r="N51" t="n">
-        <v>2.69</v>
+        <v>7.03</v>
       </c>
       <c r="O51" t="n">
         <v>-1.79</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46171.38541666666</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1840.1</v>
+        <v>1803.5</v>
       </c>
       <c r="I52" t="n">
         <v>1822.087556875167</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>5.95</v>
+        <v>3.84</v>
       </c>
       <c r="L52" t="n">
         <v>6.62</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.4</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46192.55208333334</v>
+        <v>46195.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1841</v>
+        <v>1861.5</v>
       </c>
       <c r="I53" t="n">
         <v>1848.98754877643</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.08</v>
+        <v>-3.22</v>
       </c>
       <c r="L53" t="n">
-        <v>2.22</v>
+        <v>3.26</v>
       </c>
       <c r="M53" t="n">
         <v>0.61</v>
       </c>
       <c r="N53" t="n">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="O53" t="n">
         <v>-1.98</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>3.76</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46237.38541666666</v>
+        <v>46237.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1960</v>
+        <v>1945</v>
       </c>
       <c r="I54" t="n">
         <v>1953.231753107124</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K54" t="n">
-        <v>5.29</v>
+        <v>4.49</v>
       </c>
       <c r="L54" t="n">
         <v>1.48</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3579,6 +4238,14 @@
       <c r="Q55" t="n">
         <v>119</v>
       </c>
+      <c r="R55" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5681,7 +6348,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.4</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="6">
@@ -5691,7 +6358,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -5701,7 +6368,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>130.2</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8">
@@ -5711,7 +6378,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -5721,7 +6388,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="10">
@@ -5731,7 +6398,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -5771,7 +6438,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.02</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="15">
@@ -5781,7 +6448,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.95</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="16">
@@ -5791,7 +6458,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="17">
@@ -5801,7 +6468,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.49</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="18">
@@ -5811,7 +6478,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
@@ -5821,7 +6488,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="20">
@@ -5831,7 +6498,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.57</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="21">
@@ -5841,7 +6508,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.31</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -5851,7 +6518,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -5871,7 +6538,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.08</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="25">
@@ -5881,7 +6548,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.53</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="26">
@@ -5891,7 +6558,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.19</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="27">
@@ -5901,7 +6568,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.51</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="28">
@@ -5911,7 +6578,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
